--- a/public/LinearModuleASF.xlsx
+++ b/public/LinearModuleASF.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ЭтаКнига" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ru0nntr\Desktop\Прочее\Linear Motion Calculator\project_v0.96\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ru0nntr\Desktop\Прочее\Linear Motion Calculator\project_v0.97\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="95">
   <si>
     <t>ITO40</t>
   </si>
@@ -297,6 +297,18 @@
   </si>
   <si>
     <t>mod_GBtype</t>
+  </si>
+  <si>
+    <t>calc_meanTorque</t>
+  </si>
+  <si>
+    <t>calc_meanRPM</t>
+  </si>
+  <si>
+    <t>mod_GB_idleTorque</t>
+  </si>
+  <si>
+    <t>mod_GB_inertia</t>
   </si>
 </sst>
 </file>
@@ -626,7 +638,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -636,7 +648,7 @@
     <col min="23" max="23" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -712,8 +724,20 @@
       <c r="Y1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -777,8 +801,14 @@
       <c r="Y2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB2">
+        <v>0.05</v>
+      </c>
+      <c r="AC2">
+        <v>1.5999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -842,8 +872,14 @@
       <c r="Y3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB3">
+        <v>0.1</v>
+      </c>
+      <c r="AC3">
+        <v>2.1999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -908,8 +944,14 @@
       <c r="Y4" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB4">
+        <v>0.1</v>
+      </c>
+      <c r="AC4">
+        <v>2.1999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -973,8 +1015,14 @@
       <c r="Y5" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB5">
+        <v>0.4</v>
+      </c>
+      <c r="AC5">
+        <v>1.7000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -1039,8 +1087,14 @@
       <c r="Y6" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB6">
+        <v>0.4</v>
+      </c>
+      <c r="AC6">
+        <v>1.7000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -1104,8 +1158,14 @@
       <c r="Y7" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB7">
+        <v>0.4</v>
+      </c>
+      <c r="AC7">
+        <v>1.7000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>65</v>
       </c>
@@ -1170,8 +1230,14 @@
       <c r="Y8" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB8">
+        <v>0.4</v>
+      </c>
+      <c r="AC8">
+        <v>1.7000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1235,8 +1301,14 @@
       <c r="Y9" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB9">
+        <v>0.4</v>
+      </c>
+      <c r="AC9">
+        <v>1.7000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -1300,8 +1372,14 @@
       <c r="Y10" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB10">
+        <v>0.1</v>
+      </c>
+      <c r="AC10">
+        <v>2.1999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -1365,8 +1443,14 @@
       <c r="Y11" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB11">
+        <v>0.4</v>
+      </c>
+      <c r="AC11">
+        <v>1.7000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -1431,8 +1515,14 @@
       <c r="Y12" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB12">
+        <v>0.4</v>
+      </c>
+      <c r="AC12">
+        <v>1.7000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>69</v>
       </c>
@@ -1496,8 +1586,14 @@
       <c r="Y13" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB13">
+        <v>0.4</v>
+      </c>
+      <c r="AC13">
+        <v>1.7000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -1527,13 +1623,13 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>216</v>
+        <v>374</v>
       </c>
       <c r="K14">
-        <v>765</v>
+        <v>2665</v>
       </c>
       <c r="L14">
-        <v>765</v>
+        <v>2665</v>
       </c>
       <c r="M14">
         <v>95</v>
@@ -1562,8 +1658,14 @@
       <c r="Y14" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB14">
+        <v>0.4</v>
+      </c>
+      <c r="AC14">
+        <v>1.7000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>71</v>
       </c>
@@ -1628,8 +1730,14 @@
       <c r="Y15" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB15">
+        <v>0.1</v>
+      </c>
+      <c r="AC15">
+        <v>1.7000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -1695,8 +1803,14 @@
       <c r="Y16" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB16">
+        <v>0.4</v>
+      </c>
+      <c r="AC16">
+        <v>1.7000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1758,8 +1872,14 @@
       <c r="X17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1821,8 +1941,14 @@
       <c r="X18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1884,8 +2010,14 @@
       <c r="X19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -1946,8 +2078,14 @@
       <c r="X20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -2008,8 +2146,14 @@
       <c r="X21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -2070,8 +2214,14 @@
       <c r="X22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -2132,8 +2282,14 @@
       <c r="X23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -2194,8 +2350,14 @@
       <c r="X24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -2256,8 +2418,14 @@
       <c r="X25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -2318,8 +2486,14 @@
       <c r="X26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2380,8 +2554,14 @@
       <c r="X27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -2442,8 +2622,14 @@
       <c r="X28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2690,14 @@
       <c r="X29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -2567,8 +2759,14 @@
       <c r="X30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>22</v>
       </c>
@@ -2630,8 +2828,14 @@
       <c r="X31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -2693,8 +2897,14 @@
       <c r="X32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -2756,8 +2966,14 @@
       <c r="X33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -2819,8 +3035,14 @@
       <c r="X34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>26</v>
       </c>
@@ -2882,8 +3104,14 @@
       <c r="X35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -2945,8 +3173,14 @@
       <c r="X36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -3008,8 +3242,14 @@
       <c r="X37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>29</v>
       </c>
@@ -3071,8 +3311,14 @@
       <c r="X38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>30</v>
       </c>
@@ -3133,8 +3379,14 @@
       <c r="X39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>31</v>
       </c>
@@ -3195,8 +3447,14 @@
       <c r="X40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -3257,8 +3515,14 @@
       <c r="X41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>33</v>
       </c>
@@ -3320,8 +3584,14 @@
       <c r="X42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -3383,8 +3653,14 @@
       <c r="X43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -3446,8 +3722,14 @@
       <c r="X44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -3509,8 +3791,14 @@
       <c r="X45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -3572,8 +3860,14 @@
       <c r="X46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>38</v>
       </c>
@@ -3635,8 +3929,14 @@
       <c r="X47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -3698,8 +3998,14 @@
       <c r="X48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>43</v>
       </c>
@@ -3761,8 +4067,14 @@
       <c r="X49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>42</v>
       </c>
@@ -3824,8 +4136,14 @@
       <c r="X50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>41</v>
       </c>
@@ -3885,6 +4203,12 @@
         <v>83</v>
       </c>
       <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
         <v>0</v>
       </c>
     </row>

--- a/public/LinearModuleASF.xlsx
+++ b/public/LinearModuleASF.xlsx
@@ -748,7 +748,7 @@
         <v>0.1</v>
       </c>
       <c r="D2">
-        <v>9.2560000000000008E-5</v>
+        <v>9.2559999999999995E-5</v>
       </c>
       <c r="E2">
         <v>9.4600000000000009E-6</v>
@@ -1818,7 +1818,7 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>0.4</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D17">
         <v>1.5E-6</v>
@@ -1887,7 +1887,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="D18">
         <v>1.5E-6</v>
@@ -1956,7 +1956,7 @@
         <v>20</v>
       </c>
       <c r="C19">
-        <v>0.4</v>
+        <v>0.09</v>
       </c>
       <c r="D19">
         <v>1.5E-6</v>
@@ -2025,7 +2025,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="D20">
         <v>9.9999999999999991E-6</v>
@@ -2093,7 +2093,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.75</v>
+        <v>0.12</v>
       </c>
       <c r="D21">
         <v>9.9999999999999991E-6</v>
@@ -2161,7 +2161,7 @@
         <v>20</v>
       </c>
       <c r="C22">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="D22">
         <v>9.9999999999999991E-6</v>
@@ -2229,7 +2229,7 @@
         <v>32</v>
       </c>
       <c r="C23">
-        <v>0.75</v>
+        <v>0.17</v>
       </c>
       <c r="D23">
         <v>9.9999999999999991E-6</v>
@@ -2297,7 +2297,7 @@
         <v>5</v>
       </c>
       <c r="C24">
-        <v>1.3</v>
+        <v>0.12</v>
       </c>
       <c r="D24">
         <v>6.4459999999999989E-5</v>
@@ -2365,7 +2365,7 @@
         <v>10</v>
       </c>
       <c r="C25">
-        <v>1.3</v>
+        <v>0.15</v>
       </c>
       <c r="D25">
         <v>6.4459999999999989E-5</v>
@@ -2433,7 +2433,7 @@
         <v>20</v>
       </c>
       <c r="C26">
-        <v>1.3</v>
+        <v>0.17</v>
       </c>
       <c r="D26">
         <v>6.4459999999999989E-5</v>
@@ -2501,7 +2501,7 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>1.3</v>
+        <v>0.19</v>
       </c>
       <c r="D27">
         <v>6.4459999999999989E-5</v>

--- a/public/LinearModuleASF.xlsx
+++ b/public/LinearModuleASF.xlsx
@@ -185,21 +185,6 @@
     <t>mod_pic</t>
   </si>
   <si>
-    <t>https://smarta.ru/upload/resize_cache/iblock/040/ep8pn4jto5au0a5ymsd3p326uxudj5l1/649_393_2/ITC.png</t>
-  </si>
-  <si>
-    <t>https://smarta.ru/upload/resize_cache/iblock/2d4/8bltm7c7edndleb5qt6ap06fmouw9q4g/618_452_2/GTC_80_SMARTA.png</t>
-  </si>
-  <si>
-    <t>https://smarta.ru/upload/resize_cache/iblock/8d0/wnxrj1xo08hboz7v7dk8rcfiu1s3v1sl/682_408_2/GSC_50_80.png</t>
-  </si>
-  <si>
-    <t>https://smarta.ru/upload/resize_cache/iblock/28b/hh11io00vis73zwwkng3i5lkrida2emb/1000_650_2/GSC_120.png</t>
-  </si>
-  <si>
-    <t>https://smarta.ru/upload/iblock/2b1/ynpg6ux0t9ui36qgk8qsfz9vrs3hsqsp/LMC_S_1.png</t>
-  </si>
-  <si>
     <t>mod_maxSpeed</t>
   </si>
   <si>
@@ -245,15 +230,6 @@
     <t>HTZ80</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/cLTHzQ7y/ITO160.png</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/pLkTSDQt/HTZ60-80.png</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/g24J7vVt/HTO60-80-100.png</t>
-  </si>
-  <si>
     <t>calc_GSL</t>
   </si>
   <si>
@@ -309,6 +285,30 @@
   </si>
   <si>
     <t>mod_GB_inertia</t>
+  </si>
+  <si>
+    <t>./pics/itc.png</t>
+  </si>
+  <si>
+    <t>./pics/ito_160.png</t>
+  </si>
+  <si>
+    <t>./pics/hto.png</t>
+  </si>
+  <si>
+    <t>./pics/htz-60_80.png</t>
+  </si>
+  <si>
+    <t>./pics/gsc-50_80.png</t>
+  </si>
+  <si>
+    <t>./pics/gsc-120.png</t>
+  </si>
+  <si>
+    <t>./pics/gtc.png</t>
+  </si>
+  <si>
+    <t>./pics/lmc.png</t>
   </si>
 </sst>
 </file>
@@ -698,43 +698,43 @@
         <v>52</v>
       </c>
       <c r="Q1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="R1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="S1" t="s">
+        <v>68</v>
+      </c>
+      <c r="T1" t="s">
+        <v>69</v>
+      </c>
+      <c r="U1" t="s">
+        <v>70</v>
+      </c>
+      <c r="V1" t="s">
         <v>76</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X1" t="s">
         <v>77</v>
       </c>
-      <c r="U1" t="s">
-        <v>78</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA1" t="s">
         <v>84</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AB1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC1" t="s">
         <v>86</v>
-      </c>
-      <c r="X1" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
@@ -784,7 +784,7 @@
         <v>20</v>
       </c>
       <c r="P2" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -793,13 +793,13 @@
         <v>50</v>
       </c>
       <c r="W2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="X2">
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AB2">
         <v>0.05</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <v>130</v>
@@ -855,7 +855,7 @@
         <v>40</v>
       </c>
       <c r="P3" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -864,13 +864,13 @@
         <v>50</v>
       </c>
       <c r="W3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X3">
         <v>1</v>
       </c>
       <c r="Y3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AB3">
         <v>0.1</v>
@@ -881,7 +881,7 @@
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B4">
         <v>130</v>
@@ -927,7 +927,7 @@
         <v>40</v>
       </c>
       <c r="P4" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -936,13 +936,13 @@
         <v>50</v>
       </c>
       <c r="W4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X4">
         <v>1</v>
       </c>
       <c r="Y4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AB4">
         <v>0.1</v>
@@ -953,7 +953,7 @@
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B5">
         <v>176</v>
@@ -998,7 +998,7 @@
         <v>50</v>
       </c>
       <c r="P5" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -1007,13 +1007,13 @@
         <v>50</v>
       </c>
       <c r="W5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AB5">
         <v>0.4</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B6">
         <v>176</v>
@@ -1070,7 +1070,7 @@
         <v>50</v>
       </c>
       <c r="P6" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -1079,13 +1079,13 @@
         <v>50</v>
       </c>
       <c r="W6" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AB6">
         <v>0.4</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B7">
         <v>224</v>
@@ -1141,7 +1141,7 @@
         <v>65</v>
       </c>
       <c r="P7" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -1150,13 +1150,13 @@
         <v>50</v>
       </c>
       <c r="W7" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AB7">
         <v>0.4</v>
@@ -1167,7 +1167,7 @@
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B8">
         <v>224</v>
@@ -1213,7 +1213,7 @@
         <v>65</v>
       </c>
       <c r="P8" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -1222,13 +1222,13 @@
         <v>50</v>
       </c>
       <c r="W8" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X8">
         <v>1</v>
       </c>
       <c r="Y8" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AB8">
         <v>0.4</v>
@@ -1284,7 +1284,7 @@
         <v>40</v>
       </c>
       <c r="P9" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -1293,13 +1293,13 @@
         <v>50</v>
       </c>
       <c r="W9" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
       <c r="Y9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AB9">
         <v>0.4</v>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B10">
         <v>130</v>
@@ -1355,7 +1355,7 @@
         <v>40</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -1364,13 +1364,13 @@
         <v>50</v>
       </c>
       <c r="W10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X10">
         <v>1</v>
       </c>
       <c r="Y10" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AB10">
         <v>0.1</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B11">
         <v>176</v>
@@ -1426,7 +1426,7 @@
         <v>50</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -1435,13 +1435,13 @@
         <v>50</v>
       </c>
       <c r="W11" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X11">
         <v>1</v>
       </c>
       <c r="Y11" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AB11">
         <v>0.4</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B12">
         <v>176</v>
@@ -1498,7 +1498,7 @@
         <v>50</v>
       </c>
       <c r="P12" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="Q12">
         <v>5</v>
@@ -1507,13 +1507,13 @@
         <v>50</v>
       </c>
       <c r="W12" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X12">
         <v>1</v>
       </c>
       <c r="Y12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AB12">
         <v>0.4</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B13">
         <v>224</v>
@@ -1569,7 +1569,7 @@
         <v>65</v>
       </c>
       <c r="P13" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -1578,13 +1578,13 @@
         <v>50</v>
       </c>
       <c r="W13" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X13">
         <v>1</v>
       </c>
       <c r="Y13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AB13">
         <v>0.4</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <v>224</v>
@@ -1641,7 +1641,7 @@
         <v>65</v>
       </c>
       <c r="P14" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="Q14">
         <v>5</v>
@@ -1650,13 +1650,13 @@
         <v>50</v>
       </c>
       <c r="W14" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X14">
         <v>1</v>
       </c>
       <c r="Y14" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AB14">
         <v>0.4</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B15">
         <v>130</v>
@@ -1713,7 +1713,7 @@
         <v>40</v>
       </c>
       <c r="P15" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -1722,13 +1722,13 @@
         <v>50</v>
       </c>
       <c r="W15" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AB15">
         <v>0.1</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B16">
         <v>210</v>
@@ -1786,7 +1786,7 @@
         <v>50</v>
       </c>
       <c r="P16" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="Q16">
         <v>5</v>
@@ -1795,13 +1795,13 @@
         <v>50</v>
       </c>
       <c r="W16" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
       <c r="Y16" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AB16">
         <v>0.4</v>
@@ -1858,7 +1858,7 @@
         <v>30</v>
       </c>
       <c r="P17" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="Q17">
         <v>0.25</v>
@@ -1927,7 +1927,7 @@
         <v>30</v>
       </c>
       <c r="P18" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="Q18">
         <v>0.5</v>
@@ -1996,7 +1996,7 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="Q19">
         <v>1</v>
@@ -2064,7 +2064,7 @@
         <v>40</v>
       </c>
       <c r="P20" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="Q20">
         <v>0.25</v>
@@ -2132,7 +2132,7 @@
         <v>40</v>
       </c>
       <c r="P21" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="Q21">
         <v>0.5</v>
@@ -2141,7 +2141,7 @@
         <v>15</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X21">
         <v>0</v>
@@ -2200,7 +2200,7 @@
         <v>40</v>
       </c>
       <c r="P22" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="Q22">
         <v>1</v>
@@ -2209,7 +2209,7 @@
         <v>25</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X22">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>40</v>
       </c>
       <c r="P23" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="Q23">
         <v>1.6</v>
@@ -2277,7 +2277,7 @@
         <v>30</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X23">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>35</v>
       </c>
       <c r="P24" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="Q24">
         <v>0.25</v>
@@ -2345,7 +2345,7 @@
         <v>5</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X24">
         <v>0</v>
@@ -2404,7 +2404,7 @@
         <v>35</v>
       </c>
       <c r="P25" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="Q25">
         <v>0.5</v>
@@ -2413,7 +2413,7 @@
         <v>15</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X25">
         <v>0</v>
@@ -2472,7 +2472,7 @@
         <v>35</v>
       </c>
       <c r="P26" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="Q26">
         <v>1</v>
@@ -2481,7 +2481,7 @@
         <v>25</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X26">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>35</v>
       </c>
       <c r="P27" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="Q27">
         <v>1.6</v>
@@ -2549,7 +2549,7 @@
         <v>30</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X27">
         <v>0</v>
@@ -2608,7 +2608,7 @@
         <v>30</v>
       </c>
       <c r="P28" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="Q28">
         <v>2</v>
@@ -2676,7 +2676,7 @@
         <v>40</v>
       </c>
       <c r="P29" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="Q29">
         <v>2.4</v>
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q30">
         <v>0.25</v>
@@ -2754,7 +2754,7 @@
         <v>5</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="X30">
         <v>0</v>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q31">
         <v>0.5</v>
@@ -2823,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="X31">
         <v>0</v>
@@ -2883,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q32">
         <v>1</v>
@@ -2892,7 +2892,7 @@
         <v>15</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="X32">
         <v>0</v>
@@ -2952,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q33">
         <v>0.25</v>
@@ -2961,7 +2961,7 @@
         <v>5</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="X33">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q34">
         <v>0.5</v>
@@ -3030,7 +3030,7 @@
         <v>10</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="X34">
         <v>0</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q35">
         <v>1</v>
@@ -3099,7 +3099,7 @@
         <v>15</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="X35">
         <v>0</v>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q36">
         <v>0.25</v>
@@ -3168,7 +3168,7 @@
         <v>5</v>
       </c>
       <c r="W36" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X36">
         <v>0</v>
@@ -3228,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q37">
         <v>0.5</v>
@@ -3237,7 +3237,7 @@
         <v>10</v>
       </c>
       <c r="W37" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X37">
         <v>0</v>
@@ -3297,7 +3297,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q38">
         <v>1</v>
@@ -3306,7 +3306,7 @@
         <v>15</v>
       </c>
       <c r="W38" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X38">
         <v>0</v>
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q39">
         <v>0.25</v>
@@ -3374,7 +3374,7 @@
         <v>5</v>
       </c>
       <c r="W39" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X39">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q40">
         <v>0.5</v>
@@ -3442,7 +3442,7 @@
         <v>15</v>
       </c>
       <c r="W40" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X40">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q41">
         <v>1</v>
@@ -3510,7 +3510,7 @@
         <v>25</v>
       </c>
       <c r="W41" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="X41">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q42">
         <v>0.25</v>
@@ -3579,7 +3579,7 @@
         <v>5</v>
       </c>
       <c r="W42" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X42">
         <v>0</v>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q43">
         <v>0.5</v>
@@ -3648,7 +3648,7 @@
         <v>15</v>
       </c>
       <c r="W43" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X43">
         <v>0</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3717,7 +3717,7 @@
         <v>25</v>
       </c>
       <c r="W44" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X44">
         <v>0</v>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q45">
         <v>0.25</v>
@@ -3846,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q46">
         <v>0.5</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q47">
         <v>1</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q48">
         <v>1.2</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q49">
         <v>0.5</v>
@@ -4062,7 +4062,7 @@
         <v>15</v>
       </c>
       <c r="W49" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="X49">
         <v>0</v>
@@ -4122,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -4131,7 +4131,7 @@
         <v>25</v>
       </c>
       <c r="W50" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="X50">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4200,7 +4200,7 @@
         <v>35</v>
       </c>
       <c r="W51" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="X51">
         <v>0</v>
